--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:46</t>
+    <t xml:space="preserve">2026-09-09 23:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:46</t>
+    <t xml:space="preserve">2026-09-18 10:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:34</t>
+    <t xml:space="preserve">2026-09-23 13:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 13:07</t>
+    <t xml:space="preserve">2026-10-02 15:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:27</t>
+    <t xml:space="preserve">2026-10-05 13:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1113,7 +1113,7 @@
         <v>2020</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>110065.62</v>
+        <v>110065.63</v>
       </c>
     </row>
     <row r="31">
@@ -1198,7 +1198,7 @@
         <v>2020</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>109329.12</v>
+        <v>109329.13</v>
       </c>
     </row>
     <row r="36">
